--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,180 +19,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
-  <x:si>
-    <x:t>인사팀장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 뇌세포 자극과 치매 예방을 위해 가상현실 VR 전투 프로그램인 'H.B. 프로젝트'를 정기적으로 가동해야 하네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네가 돌볼 분들은 평범한 어르신들이 아니라네. 한때 세계를 구했던 ‘전설의 초인들’이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <x:si>
+    <x:t>보상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sub</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestClass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Num</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>Content</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>어르신들이 가상현실 속에서 전성기 시절의 스트레스를 풀 수 있도록, 자네는 뒤에서 파스나 무릎 보호대 같은 물품만 잘 서포트해 드리면 되네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정부도 감당 못 하는 영웅들의 노환을 우리 재단이 안식처가 되어 돌보는 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은퇴 사생활 보호를 위해 대외적으로는 철저히 비밀에 부쳐진 요양원이라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자네의 임무는 단순해. 우리가 전폭적인 예산과 자재를 쥐여줄 테니, 어르신들의 특성에 맞춘 안락한 방을 만들고 시설을 키우게.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나이 앞에는 장사 없지 않나. 치매, 관절염, 골다공증...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정말 숭고한 복지 사업이네요! 제가 어르신들을 위해 정확히 어떤 일을 하면 될까요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>축하하네. 우리 H.A.V.E.N.(Heroes Aftercare &amp; Vitality Extension Network) 재단의 신입 요양보조사로 합격한 것을.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말단 직원이 왜 건설까지 해야 하나' 싶겠지만, 다 어르신들의 사생활을 완벽히 격리하고 보호하기 위한 우리 재단의 방침이니 유념하고.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 많은 어르신을 모실수록 재단은 기뻐할 걸세.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 더 지어서 더 많은 어르신을 모신다...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_17</x:t>
-  </x:si>
-  <x:si>
     <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Speaker</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Content</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최선을 다해 케어하겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어르신들의 잊혀진 기억을 되찾아드리는 VR 프로그램이라니, 정말 감동적입니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좋은 요양원을 짓는 일이라면 벽돌이라도 기쁘게 나르겠습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그런데 왜 그런 대단한 영웅들이 이런 시골 요양원에 계신 거죠?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음, 대외적으로는 Heroes Best Project의 약자라네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{PlayerName}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B. 프로젝트요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Opening_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하하, 아주 좋아. 그리고 가장 중요한 업무가 있네.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외계 침공을 막아내던 그 히어로분들이요?!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아주 안전하고 유익한 복지 프로그램이지.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextID</x:t>
+    <x:t>첫 출근 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Reward</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 출근 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초기 입소 영웅 3명과 대화하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요양보조사 사무실 건설</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 지원금 수령하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_1_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어르신 문안 인사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_1_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_1_03</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -339,7 +246,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -387,6 +294,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -992,104 +905,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:Q35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="13.85546875" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="120" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.54296875" style="3"/>
+    <x:col min="3" max="3" width="50.71484375" style="3" customWidth="1"/>
+    <x:col min="4" max="6" width="15.85546875" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="30.54296875" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="26.54296875" style="3" customWidth="1"/>
+    <x:col min="9" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
+      <x:c r="C2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:8" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="s">
+      <x:c r="B3" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="10" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D3" s="12" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="D3" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G3" s="12"/>
+      <x:c r="H3" s="13"/>
+    </x:row>
+    <x:row r="4" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="14"/>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
+        <x:v>500</x:v>
+      </x:c>
       <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
+      <x:c r="H4" s="14"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1097,24 +1010,30 @@
       <x:c r="M4" s="5"/>
       <x:c r="N4" s="5"/>
       <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="5"/>
+      <x:c r="Q4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="14"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:v>500</x:v>
+      </x:c>
       <x:c r="G5" s="5"/>
-      <x:c r="H5" s="5"/>
+      <x:c r="H5" s="14"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
       <x:c r="K5" s="5"/>
@@ -1122,22 +1041,28 @@
       <x:c r="M5" s="5"/>
       <x:c r="N5" s="5"/>
       <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>47</x:v>
+      <x:c r="P5" s="5"/>
+      <x:c r="Q5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A6" s="4" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F6" s="5">
+        <x:v>500</x:v>
+      </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
@@ -1147,21 +1072,15 @@
       <x:c r="M6" s="5"/>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E7" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A7" s="4"/>
+      <x:c r="B7" s="4"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6"/>
       <x:c r="F7" s="5"/>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5"/>
@@ -1172,22 +1091,16 @@
       <x:c r="M7" s="5"/>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="6" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
+      <x:c r="P7" s="5"/>
+      <x:c r="Q7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A8" s="4"/>
+      <x:c r="B8" s="4"/>
+      <x:c r="C8" s="4"/>
+      <x:c r="D8" s="16"/>
+      <x:c r="E8" s="16"/>
+      <x:c r="F8" s="15"/>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
@@ -1197,21 +1110,15 @@
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B9" s="4" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E9" s="5"/>
+      <x:c r="P8" s="5"/>
+      <x:c r="Q8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A9" s="4"/>
+      <x:c r="B9" s="4"/>
+      <x:c r="C9" s="4"/>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
       <x:c r="F9" s="5"/>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5"/>
@@ -1222,21 +1129,15 @@
       <x:c r="M9" s="5"/>
       <x:c r="N9" s="5"/>
       <x:c r="O9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="6" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B10" s="4" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C10" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E10" s="5"/>
+      <x:c r="P9" s="5"/>
+      <x:c r="Q9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A10" s="4"/>
+      <x:c r="B10" s="4"/>
+      <x:c r="C10" s="4"/>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
       <x:c r="F10" s="5"/>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
@@ -1247,22 +1148,16 @@
       <x:c r="M10" s="5"/>
       <x:c r="N10" s="5"/>
       <x:c r="O10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="6" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B11" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
+      <x:c r="P10" s="5"/>
+      <x:c r="Q10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="6"/>
+      <x:c r="D11" s="17"/>
+      <x:c r="E11" s="17"/>
+      <x:c r="F11" s="15"/>
       <x:c r="G11" s="5"/>
       <x:c r="H11" s="5"/>
       <x:c r="I11" s="5"/>
@@ -1272,22 +1167,16 @@
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B12" s="4" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C12" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
+      <x:c r="P11" s="5"/>
+      <x:c r="Q11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A12" s="4"/>
+      <x:c r="B12" s="4"/>
+      <x:c r="C12" s="4"/>
+      <x:c r="D12" s="16"/>
+      <x:c r="E12" s="16"/>
+      <x:c r="F12" s="15"/>
       <x:c r="G12" s="5"/>
       <x:c r="H12" s="5"/>
       <x:c r="I12" s="5"/>
@@ -1297,21 +1186,15 @@
       <x:c r="M12" s="5"/>
       <x:c r="N12" s="5"/>
       <x:c r="O12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B13" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C13" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E13" s="5"/>
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A13" s="4"/>
+      <x:c r="B13" s="4"/>
+      <x:c r="C13" s="4"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
       <x:c r="F13" s="5"/>
       <x:c r="G13" s="5"/>
       <x:c r="H13" s="5"/>
@@ -1322,21 +1205,15 @@
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="6" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E14" s="5"/>
+      <x:c r="P13" s="5"/>
+      <x:c r="Q13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A14" s="6"/>
+      <x:c r="B14" s="4"/>
+      <x:c r="C14" s="4"/>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
       <x:c r="F14" s="5"/>
       <x:c r="G14" s="5"/>
       <x:c r="H14" s="5"/>
@@ -1347,22 +1224,16 @@
       <x:c r="M14" s="5"/>
       <x:c r="N14" s="5"/>
       <x:c r="O14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="6" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B15" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
+      <x:c r="P14" s="5"/>
+      <x:c r="Q14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:17" ht="15.75" customHeight="1">
+      <x:c r="A15" s="6"/>
+      <x:c r="B15" s="4"/>
+      <x:c r="C15" s="6"/>
+      <x:c r="D15" s="17"/>
+      <x:c r="E15" s="17"/>
+      <x:c r="F15" s="15"/>
       <x:c r="G15" s="5"/>
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
@@ -1372,192 +1243,162 @@
       <x:c r="M15" s="5"/>
       <x:c r="N15" s="5"/>
       <x:c r="O15" s="5"/>
-    </x:row>
-    <x:row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A16" s="6" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B16" s="4" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D16" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B17" s="4" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C17" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A18" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B18" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="6" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C19" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A20" s="6" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B20" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C20" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A21" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C21" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A22" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B22" s="4" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C22" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="5" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A23" s="6" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B23" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C23" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A24" s="6" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B24" s="7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D24" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="P15" s="5"/>
+      <x:c r="Q15" s="5"/>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A16" s="6"/>
+      <x:c r="B16" s="4"/>
+      <x:c r="C16" s="6"/>
+      <x:c r="D16" s="6"/>
+      <x:c r="E16" s="6"/>
+      <x:c r="F16" s="5"/>
+    </x:row>
+    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A17" s="6"/>
+      <x:c r="B17" s="4"/>
+      <x:c r="C17" s="4"/>
+      <x:c r="D17" s="16"/>
+      <x:c r="E17" s="16"/>
+      <x:c r="F17" s="15"/>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A18" s="6"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="5"/>
+    </x:row>
+    <x:row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A19" s="6"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="6"/>
+      <x:c r="D19" s="17"/>
+      <x:c r="E19" s="17"/>
+      <x:c r="F19" s="15"/>
+      <x:c r="G19" s="5"/>
+    </x:row>
+    <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A20" s="6"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="16"/>
+      <x:c r="E20" s="16"/>
+      <x:c r="F20" s="15"/>
+    </x:row>
+    <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A21" s="6"/>
+      <x:c r="B21" s="4"/>
+      <x:c r="C21" s="4"/>
+      <x:c r="D21" s="4"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="5"/>
+    </x:row>
+    <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A22" s="6"/>
+      <x:c r="B22" s="4"/>
+      <x:c r="C22" s="4"/>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="5"/>
+    </x:row>
+    <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A23" s="6"/>
+      <x:c r="B23" s="4"/>
+      <x:c r="C23" s="6"/>
+      <x:c r="D23" s="17"/>
+      <x:c r="E23" s="17"/>
+      <x:c r="F23" s="15"/>
+    </x:row>
+    <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A24" s="6"/>
+      <x:c r="B24" s="7"/>
+      <x:c r="C24" s="6"/>
+      <x:c r="D24" s="6"/>
+      <x:c r="E24" s="6"/>
+      <x:c r="F24" s="5"/>
+    </x:row>
+    <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A25" s="7"/>
       <x:c r="B25" s="7"/>
       <x:c r="C25" s="7"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D25" s="7"/>
+      <x:c r="E25" s="7"/>
+      <x:c r="G25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A26" s="8"/>
       <x:c r="B26" s="8"/>
       <x:c r="C26" s="8"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D26" s="8"/>
+      <x:c r="E26" s="8"/>
+      <x:c r="G26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A27" s="8"/>
       <x:c r="B27" s="8"/>
       <x:c r="C27" s="8"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D27" s="8"/>
+      <x:c r="E27" s="8"/>
+      <x:c r="G27" s="5"/>
+    </x:row>
+    <x:row r="28" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A28" s="8"/>
       <x:c r="B28" s="8"/>
       <x:c r="C28" s="8"/>
-      <x:c r="E28" s="5"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D28" s="8"/>
+      <x:c r="E28" s="8"/>
+      <x:c r="G28" s="5"/>
+    </x:row>
+    <x:row r="29" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A29" s="8"/>
       <x:c r="B29" s="8"/>
       <x:c r="C29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D29" s="8"/>
+      <x:c r="E29" s="8"/>
+    </x:row>
+    <x:row r="30" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A30" s="8"/>
       <x:c r="B30" s="8"/>
       <x:c r="C30" s="8"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D30" s="8"/>
+      <x:c r="E30" s="8"/>
+    </x:row>
+    <x:row r="31" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A31" s="8"/>
       <x:c r="B31" s="8"/>
       <x:c r="C31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D31" s="8"/>
+      <x:c r="E31" s="8"/>
+    </x:row>
+    <x:row r="32" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A32" s="9"/>
       <x:c r="B32" s="9"/>
       <x:c r="C32" s="9"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D32" s="9"/>
+      <x:c r="E32" s="9"/>
+    </x:row>
+    <x:row r="33" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A33" s="9"/>
       <x:c r="B33" s="9"/>
       <x:c r="C33" s="9"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D33" s="9"/>
+      <x:c r="E33" s="9"/>
+    </x:row>
+    <x:row r="34" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A34" s="9"/>
       <x:c r="B34" s="9"/>
       <x:c r="C34" s="9"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D34" s="9"/>
+      <x:c r="E34" s="9"/>
+    </x:row>
+    <x:row r="35" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A35" s="9"/>
       <x:c r="B35" s="9"/>
       <x:c r="C35" s="9"/>
+      <x:c r="D35" s="9"/>
+      <x:c r="E35" s="9"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <x:si>
     <x:t>int</x:t>
   </x:si>
@@ -27,19 +27,70 @@
     <x:t>ID</x:t>
   </x:si>
   <x:si>
-    <x:t>AdmitHero</x:t>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
   </x:si>
   <x:si>
     <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
 사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
   </x:si>
   <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
     <x:t>영웅들이 지낼 방이 필요합니다.
 침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -109,16 +160,13 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_01_03</x:t>
@@ -127,34 +175,56 @@
     <x:t>Room_Office</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
-  </x:si>
-  <x:si>
     <x:t>Quest_01_02</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>영웅들과의 만남</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Sleep</x:t>
   </x:si>
   <x:si>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
     <x:t>QuestName</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
+    <x:r>
+      <x:t xml:space="preserve">첫 삽을 뜨다 </x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="Times New Roman"/>
+            <x:sz val="10"/>
+            <x:color rgb="ff000000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="Times New Roman"/>
+            <x:sz val="10"/>
+            <x:color rgb="ff000000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>2</x:t>
+    </x:r>
   </x:si>
   <x:si>
     <x:r>
@@ -193,74 +263,17 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:t xml:space="preserve">첫 삽을 뜨다 </x:t>
-    </x:r>
-    <x:r>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-          <x:rPr hs:extension="1">
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-            <hs:size val="100"/>
-            <hs:ratio val="100"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:rPr>
-        </mc:Choice>
-        <mc:Fallback>
-          <x:rPr>
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <x:t>2</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들의 일정 관리 또한 당신의 업무!
+하루의 일정을 정해봅시다!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1031,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:T35"/>
+  <x:dimension ref="A1:T36"/>
   <x:sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="17.83984375" style="1" customWidth="1"/>
@@ -1047,61 +1060,61 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
@@ -1111,53 +1124,53 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="s">
+      <x:c r="G3" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J3" s="8"/>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1177,31 +1190,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>5</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1217,29 +1230,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1253,30 +1266,32 @@
       <x:c r="S6" s="12"/>
       <x:c r="T6" s="12"/>
     </x:row>
-    <x:row r="7" spans="1:20" ht="32.25" customHeight="1">
+    <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C7" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H7" s="2">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="I7" s="12"/>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
       <x:c r="L7" s="12"/>
@@ -1289,16 +1304,30 @@
       <x:c r="S7" s="12"/>
       <x:c r="T7" s="12"/>
     </x:row>
-    <x:row r="8" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A8" s="2"/>
-      <x:c r="B8" s="2"/>
-      <x:c r="C8" s="2"/>
-      <x:c r="D8" s="14"/>
-      <x:c r="E8" s="14"/>
-      <x:c r="F8" s="14"/>
-      <x:c r="G8" s="14"/>
-      <x:c r="H8" s="14"/>
-      <x:c r="I8" s="15"/>
+    <x:row r="8" spans="1:20" ht="32.25" customHeight="1">
+      <x:c r="A8" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H8" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I8" s="12"/>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
       <x:c r="L8" s="12"/>
@@ -1315,12 +1344,12 @@
       <x:c r="A9" s="2"/>
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2"/>
-      <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="2"/>
-      <x:c r="I9" s="12"/>
+      <x:c r="D9" s="14"/>
+      <x:c r="E9" s="14"/>
+      <x:c r="F9" s="14"/>
+      <x:c r="G9" s="14"/>
+      <x:c r="H9" s="14"/>
+      <x:c r="I9" s="15"/>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
       <x:c r="L9" s="12"/>
@@ -1359,12 +1388,12 @@
       <x:c r="A11" s="2"/>
       <x:c r="B11" s="2"/>
       <x:c r="C11" s="2"/>
-      <x:c r="D11" s="14"/>
-      <x:c r="E11" s="14"/>
-      <x:c r="F11" s="14"/>
-      <x:c r="G11" s="14"/>
-      <x:c r="H11" s="14"/>
-      <x:c r="I11" s="15"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+      <x:c r="I11" s="12"/>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
       <x:c r="L11" s="12"/>
@@ -1403,12 +1432,12 @@
       <x:c r="A13" s="2"/>
       <x:c r="B13" s="2"/>
       <x:c r="C13" s="2"/>
-      <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
-      <x:c r="H13" s="2"/>
-      <x:c r="I13" s="12"/>
+      <x:c r="D13" s="14"/>
+      <x:c r="E13" s="14"/>
+      <x:c r="F13" s="14"/>
+      <x:c r="G13" s="14"/>
+      <x:c r="H13" s="14"/>
+      <x:c r="I13" s="15"/>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
       <x:c r="L13" s="12"/>
@@ -1447,12 +1476,12 @@
       <x:c r="A15" s="2"/>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
-      <x:c r="D15" s="14"/>
-      <x:c r="E15" s="14"/>
-      <x:c r="F15" s="14"/>
-      <x:c r="G15" s="14"/>
-      <x:c r="H15" s="14"/>
-      <x:c r="I15" s="15"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+      <x:c r="I15" s="12"/>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
       <x:c r="L15" s="12"/>
@@ -1465,52 +1494,62 @@
       <x:c r="S15" s="12"/>
       <x:c r="T15" s="12"/>
     </x:row>
-    <x:row r="16" spans="1:9" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2"/>
       <x:c r="B16" s="2"/>
       <x:c r="C16" s="2"/>
-      <x:c r="D16" s="2"/>
-      <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-      <x:c r="G16" s="2"/>
-      <x:c r="H16" s="2"/>
-      <x:c r="I16" s="12"/>
+      <x:c r="D16" s="14"/>
+      <x:c r="E16" s="14"/>
+      <x:c r="F16" s="14"/>
+      <x:c r="G16" s="14"/>
+      <x:c r="H16" s="14"/>
+      <x:c r="I16" s="15"/>
+      <x:c r="J16" s="12"/>
+      <x:c r="K16" s="12"/>
+      <x:c r="L16" s="12"/>
+      <x:c r="M16" s="12"/>
+      <x:c r="N16" s="12"/>
+      <x:c r="O16" s="12"/>
+      <x:c r="P16" s="12"/>
+      <x:c r="Q16" s="12"/>
+      <x:c r="R16" s="12"/>
+      <x:c r="S16" s="12"/>
+      <x:c r="T16" s="12"/>
     </x:row>
     <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A17" s="2"/>
       <x:c r="B17" s="2"/>
       <x:c r="C17" s="2"/>
-      <x:c r="D17" s="14"/>
-      <x:c r="E17" s="14"/>
-      <x:c r="F17" s="14"/>
-      <x:c r="G17" s="14"/>
-      <x:c r="H17" s="14"/>
-      <x:c r="I17" s="15"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+      <x:c r="I17" s="12"/>
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2"/>
       <x:c r="B18" s="2"/>
       <x:c r="C18" s="2"/>
-      <x:c r="D18" s="2"/>
-      <x:c r="E18" s="2"/>
-      <x:c r="F18" s="2"/>
-      <x:c r="G18" s="2"/>
-      <x:c r="H18" s="2"/>
-      <x:c r="I18" s="12"/>
-    </x:row>
-    <x:row r="19" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="D18" s="14"/>
+      <x:c r="E18" s="14"/>
+      <x:c r="F18" s="14"/>
+      <x:c r="G18" s="14"/>
+      <x:c r="H18" s="14"/>
+      <x:c r="I18" s="15"/>
+    </x:row>
+    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2"/>
       <x:c r="B19" s="2"/>
       <x:c r="C19" s="2"/>
-      <x:c r="D19" s="14"/>
-      <x:c r="E19" s="14"/>
-      <x:c r="F19" s="14"/>
-      <x:c r="G19" s="14"/>
-      <x:c r="H19" s="14"/>
-      <x:c r="I19" s="15"/>
-      <x:c r="J19" s="12"/>
-    </x:row>
-    <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+      <x:c r="I19" s="12"/>
+    </x:row>
+    <x:row r="20" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A20" s="2"/>
       <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
@@ -1520,17 +1559,18 @@
       <x:c r="G20" s="14"/>
       <x:c r="H20" s="14"/>
       <x:c r="I20" s="15"/>
+      <x:c r="J20" s="12"/>
     </x:row>
     <x:row r="21" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A21" s="2"/>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
-      <x:c r="D21" s="2"/>
-      <x:c r="E21" s="2"/>
-      <x:c r="F21" s="2"/>
-      <x:c r="G21" s="2"/>
-      <x:c r="H21" s="2"/>
-      <x:c r="I21" s="12"/>
+      <x:c r="D21" s="14"/>
+      <x:c r="E21" s="14"/>
+      <x:c r="F21" s="14"/>
+      <x:c r="G21" s="14"/>
+      <x:c r="H21" s="14"/>
+      <x:c r="I21" s="15"/>
     </x:row>
     <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A22" s="2"/>
@@ -1547,34 +1587,34 @@
       <x:c r="A23" s="2"/>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
-      <x:c r="D23" s="14"/>
-      <x:c r="E23" s="14"/>
-      <x:c r="F23" s="14"/>
-      <x:c r="G23" s="14"/>
-      <x:c r="H23" s="14"/>
-      <x:c r="I23" s="15"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+      <x:c r="I23" s="12"/>
     </x:row>
     <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A24" s="2"/>
-      <x:c r="B24" s="12"/>
+      <x:c r="B24" s="2"/>
       <x:c r="C24" s="2"/>
-      <x:c r="D24" s="2"/>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="2"/>
-      <x:c r="G24" s="2"/>
-      <x:c r="H24" s="2"/>
-      <x:c r="I24" s="12"/>
-    </x:row>
-    <x:row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A25" s="12"/>
+      <x:c r="D24" s="14"/>
+      <x:c r="E24" s="14"/>
+      <x:c r="F24" s="14"/>
+      <x:c r="G24" s="14"/>
+      <x:c r="H24" s="14"/>
+      <x:c r="I24" s="15"/>
+    </x:row>
+    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A25" s="2"/>
       <x:c r="B25" s="12"/>
-      <x:c r="C25" s="12"/>
-      <x:c r="D25" s="12"/>
-      <x:c r="E25" s="12"/>
-      <x:c r="F25" s="12"/>
-      <x:c r="G25" s="12"/>
-      <x:c r="H25" s="12"/>
-      <x:c r="J25" s="12"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+      <x:c r="I25" s="12"/>
     </x:row>
     <x:row r="26" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A26" s="12"/>
@@ -1609,7 +1649,7 @@
       <x:c r="H28" s="12"/>
       <x:c r="J28" s="12"/>
     </x:row>
-    <x:row r="29" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="29" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A29" s="12"/>
       <x:c r="B29" s="12"/>
       <x:c r="C29" s="12"/>
@@ -1618,6 +1658,7 @@
       <x:c r="F29" s="12"/>
       <x:c r="G29" s="12"/>
       <x:c r="H29" s="12"/>
+      <x:c r="J29" s="12"/>
     </x:row>
     <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A30" s="12"/>
@@ -1679,7 +1720,16 @@
       <x:c r="G35" s="12"/>
       <x:c r="H35" s="12"/>
     </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A36" s="12"/>
+      <x:c r="B36" s="12"/>
+      <x:c r="C36" s="12"/>
+      <x:c r="D36" s="12"/>
+      <x:c r="E36" s="12"/>
+      <x:c r="F36" s="12"/>
+      <x:c r="G36" s="12"/>
+      <x:c r="H36" s="12"/>
+    </x:row>
     <x:row r="37" ht="15.75" customHeight="1"/>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>
@@ -2644,8 +2694,9 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
+    <x:row r="1001" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69902777671813965" right="0.69902777671813965" top="0.75" bottom="0.75" header="0.51152777671813965" footer="0.51152777671813965"/>
+  <x:pageMargins left="0.69888889789581299" right="0.69888889789581299" top="0.75" bottom="0.75" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13725" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,78 +19,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
+  <x:si>
+    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
+사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들의 일정 관리 또한 당신의 업무!
+하루의 일정을 정해봅시다!</x:t>
   </x:si>
   <x:si>
     <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
 사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
   </x:si>
   <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -160,18 +140,39 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
     <x:t>Quest_01_01</x:t>
   </x:si>
   <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
     <x:t>BuildRoom</x:t>
   </x:si>
   <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>Room_Office</x:t>
   </x:si>
   <x:si>
@@ -181,22 +182,22 @@
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_03_01</x:t>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
   </x:si>
   <x:si>
     <x:t>영웅들과의 만남</x:t>
   </x:si>
   <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QuestName</x:t>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -227,53 +228,59 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:t xml:space="preserve">하루를 </x:t>
-    </x:r>
-    <x:r>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-          <x:rPr hs:extension="1">
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-            <hs:size val="100"/>
-            <hs:ratio val="100"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:rPr>
-        </mc:Choice>
-        <mc:Fallback>
-          <x:rPr>
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <x:t>3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="나눔고딕"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>번 마감</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들의 일정 관리 또한 당신의 업무!
-하루의 일정을 정해봅시다!</x:t>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,7 +417,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -460,6 +467,9 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1060,117 +1070,117 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="G2" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="J3" s="8"/>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C4" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1190,31 +1200,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1230,29 +1240,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="16" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1268,29 +1278,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="16" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1306,28 +1316,30 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="C8" s="16" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="I8" s="12"/>
+      <x:c r="I8" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
       <x:c r="L8" s="12"/>
@@ -1341,15 +1353,33 @@
       <x:c r="T8" s="12"/>
     </x:row>
     <x:row r="9" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A9" s="2"/>
-      <x:c r="B9" s="2"/>
-      <x:c r="C9" s="2"/>
-      <x:c r="D9" s="14"/>
-      <x:c r="E9" s="14"/>
-      <x:c r="F9" s="14"/>
-      <x:c r="G9" s="14"/>
-      <x:c r="H9" s="14"/>
-      <x:c r="I9" s="15"/>
+      <x:c r="A9" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F9" s="2">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G9" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H9" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
       <x:c r="L9" s="12"/>
@@ -1363,15 +1393,33 @@
       <x:c r="T9" s="12"/>
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2"/>
-      <x:c r="I10" s="12"/>
+      <x:c r="A10" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F10" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H10" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
       <x:c r="L10" s="12"/>
@@ -1385,15 +1433,33 @@
       <x:c r="T10" s="12"/>
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2"/>
-      <x:c r="I11" s="12"/>
+      <x:c r="A11" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H11" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
       <x:c r="L11" s="12"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="13725" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,41 +19,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
-  <x:si>
-    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
-사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
   </x:si>
   <x:si>
     <x:t>Shower</x:t>
   </x:si>
   <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
+사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
   </x:si>
   <x:si>
     <x:t>하루의 시작은 일정 관리부터!
 영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
+    <x:t>전설은 반드시 다시 쓰입니다.
+VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
   </x:si>
   <x:si>
     <x:t>영웅들의 일정 관리 또한 당신의 업무!
@@ -62,15 +145,6 @@
   <x:si>
     <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
 사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -140,64 +214,94 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
+    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
+사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
+이 모든 것은 영웅들을 위해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남</x:t>
   </x:si>
   <x:si>
     <x:t>AdvanceDay</x:t>
   </x:si>
   <x:si>
-    <x:t>QuestName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>BuildRoom</x:t>
   </x:si>
   <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
     <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schedule</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -226,61 +330,6 @@
       </mc:AlternateContent>
       <x:t>2</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -463,14 +512,14 @@
     <x:xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1054,12 +1103,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:T36"/>
+  <x:dimension ref="A1:T37"/>
   <x:sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="17.83984375" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="17.9375" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="46.51953125" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="48.85546875" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="14.5390625" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="24.28515625" style="1" customWidth="1"/>
     <x:col min="6" max="9" width="14.5390625" style="1" customWidth="1"/>
@@ -1070,117 +1119,117 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J3" s="8"/>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>26</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1200,31 +1249,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>26</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1240,29 +1289,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>24</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1278,29 +1327,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="s">
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1314,31 +1363,31 @@
       <x:c r="S7" s="12"/>
       <x:c r="T7" s="12"/>
     </x:row>
-    <x:row r="8" spans="1:20" ht="32.25" customHeight="1">
+    <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C8" s="16" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H8" s="2">
-        <x:v>800</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1352,33 +1401,31 @@
       <x:c r="S8" s="12"/>
       <x:c r="T8" s="12"/>
     </x:row>
-    <x:row r="9" spans="1:20" ht="15.75" customHeight="1">
+    <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="17" t="s">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1394,31 +1441,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1434,31 +1481,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1473,15 +1520,33 @@
       <x:c r="T11" s="12"/>
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
-      <x:c r="G12" s="14"/>
-      <x:c r="H12" s="14"/>
-      <x:c r="I12" s="15"/>
+      <x:c r="A12" s="2" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F12" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H12" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="s">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
       <x:c r="L12" s="12"/>
@@ -1494,16 +1559,34 @@
       <x:c r="S12" s="12"/>
       <x:c r="T12" s="12"/>
     </x:row>
-    <x:row r="13" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A13" s="2"/>
-      <x:c r="B13" s="2"/>
-      <x:c r="C13" s="2"/>
-      <x:c r="D13" s="14"/>
-      <x:c r="E13" s="14"/>
-      <x:c r="F13" s="14"/>
-      <x:c r="G13" s="14"/>
-      <x:c r="H13" s="14"/>
-      <x:c r="I13" s="15"/>
+    <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
+      <x:c r="A13" s="2" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F13" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H13" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
       <x:c r="L13" s="12"/>
@@ -1516,16 +1599,32 @@
       <x:c r="S13" s="12"/>
       <x:c r="T13" s="12"/>
     </x:row>
-    <x:row r="14" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2"/>
+    <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
+      <x:c r="A14" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
-      <x:c r="I14" s="12"/>
+      <x:c r="F14" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H14" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
       <x:c r="L14" s="12"/>
@@ -1539,15 +1638,31 @@
       <x:c r="T14" s="12"/>
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A15" s="2"/>
-      <x:c r="B15" s="2"/>
-      <x:c r="C15" s="2"/>
-      <x:c r="D15" s="2"/>
+      <x:c r="A15" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="2"/>
-      <x:c r="H15" s="2"/>
-      <x:c r="I15" s="12"/>
+      <x:c r="F15" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H15" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
       <x:c r="L15" s="12"/>
@@ -1564,12 +1679,12 @@
       <x:c r="A16" s="2"/>
       <x:c r="B16" s="2"/>
       <x:c r="C16" s="2"/>
-      <x:c r="D16" s="14"/>
-      <x:c r="E16" s="14"/>
-      <x:c r="F16" s="14"/>
-      <x:c r="G16" s="14"/>
-      <x:c r="H16" s="14"/>
-      <x:c r="I16" s="15"/>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+      <x:c r="I16" s="12"/>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
       <x:c r="L16" s="12"/>
@@ -1582,7 +1697,7 @@
       <x:c r="S16" s="12"/>
       <x:c r="T16" s="12"/>
     </x:row>
-    <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
+    <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2"/>
       <x:c r="B17" s="2"/>
       <x:c r="C17" s="2"/>
@@ -1591,18 +1706,29 @@
       <x:c r="F17" s="2"/>
       <x:c r="G17" s="2"/>
       <x:c r="H17" s="2"/>
-      <x:c r="I17" s="12"/>
+      <x:c r="I17" s="17"/>
+      <x:c r="J17" s="12"/>
+      <x:c r="K17" s="12"/>
+      <x:c r="L17" s="12"/>
+      <x:c r="M17" s="12"/>
+      <x:c r="N17" s="12"/>
+      <x:c r="O17" s="12"/>
+      <x:c r="P17" s="12"/>
+      <x:c r="Q17" s="12"/>
+      <x:c r="R17" s="12"/>
+      <x:c r="S17" s="12"/>
+      <x:c r="T17" s="12"/>
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2"/>
       <x:c r="B18" s="2"/>
       <x:c r="C18" s="2"/>
-      <x:c r="D18" s="14"/>
-      <x:c r="E18" s="14"/>
-      <x:c r="F18" s="14"/>
-      <x:c r="G18" s="14"/>
-      <x:c r="H18" s="14"/>
-      <x:c r="I18" s="15"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="2"/>
+      <x:c r="I18" s="12"/>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2"/>
@@ -1613,30 +1739,30 @@
       <x:c r="F19" s="2"/>
       <x:c r="G19" s="2"/>
       <x:c r="H19" s="2"/>
-      <x:c r="I19" s="12"/>
-    </x:row>
-    <x:row r="20" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="I19" s="17"/>
+    </x:row>
+    <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2"/>
       <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
-      <x:c r="D20" s="14"/>
-      <x:c r="E20" s="14"/>
-      <x:c r="F20" s="14"/>
-      <x:c r="G20" s="14"/>
-      <x:c r="H20" s="14"/>
-      <x:c r="I20" s="15"/>
-      <x:c r="J20" s="12"/>
-    </x:row>
-    <x:row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+      <x:c r="I20" s="12"/>
+    </x:row>
+    <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2"/>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
-      <x:c r="D21" s="14"/>
-      <x:c r="E21" s="14"/>
-      <x:c r="F21" s="14"/>
-      <x:c r="G21" s="14"/>
-      <x:c r="H21" s="14"/>
-      <x:c r="I21" s="15"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+      <x:c r="I21" s="17"/>
+      <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A22" s="2"/>
@@ -1647,7 +1773,7 @@
       <x:c r="F22" s="2"/>
       <x:c r="G22" s="2"/>
       <x:c r="H22" s="2"/>
-      <x:c r="I22" s="12"/>
+      <x:c r="I22" s="17"/>
     </x:row>
     <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="2"/>
@@ -1664,34 +1790,34 @@
       <x:c r="A24" s="2"/>
       <x:c r="B24" s="2"/>
       <x:c r="C24" s="2"/>
-      <x:c r="D24" s="14"/>
-      <x:c r="E24" s="14"/>
-      <x:c r="F24" s="14"/>
-      <x:c r="G24" s="14"/>
-      <x:c r="H24" s="14"/>
-      <x:c r="I24" s="15"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+      <x:c r="I24" s="12"/>
     </x:row>
     <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="2"/>
-      <x:c r="B25" s="12"/>
+      <x:c r="B25" s="2"/>
       <x:c r="C25" s="2"/>
       <x:c r="D25" s="2"/>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2"/>
       <x:c r="G25" s="2"/>
       <x:c r="H25" s="2"/>
-      <x:c r="I25" s="12"/>
-    </x:row>
-    <x:row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A26" s="12"/>
+      <x:c r="I25" s="17"/>
+    </x:row>
+    <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A26" s="2"/>
       <x:c r="B26" s="12"/>
-      <x:c r="C26" s="12"/>
-      <x:c r="D26" s="12"/>
-      <x:c r="E26" s="12"/>
-      <x:c r="F26" s="12"/>
-      <x:c r="G26" s="12"/>
-      <x:c r="H26" s="12"/>
-      <x:c r="J26" s="12"/>
+      <x:c r="C26" s="2"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+      <x:c r="I26" s="12"/>
     </x:row>
     <x:row r="27" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A27" s="12"/>
@@ -1726,7 +1852,7 @@
       <x:c r="H29" s="12"/>
       <x:c r="J29" s="12"/>
     </x:row>
-    <x:row r="30" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="30" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A30" s="12"/>
       <x:c r="B30" s="12"/>
       <x:c r="C30" s="12"/>
@@ -1735,6 +1861,7 @@
       <x:c r="F30" s="12"/>
       <x:c r="G30" s="12"/>
       <x:c r="H30" s="12"/>
+      <x:c r="J30" s="12"/>
     </x:row>
     <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A31" s="12"/>
@@ -1796,7 +1923,16 @@
       <x:c r="G36" s="12"/>
       <x:c r="H36" s="12"/>
     </x:row>
-    <x:row r="37" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A37" s="12"/>
+      <x:c r="B37" s="12"/>
+      <x:c r="C37" s="12"/>
+      <x:c r="D37" s="12"/>
+      <x:c r="E37" s="12"/>
+      <x:c r="F37" s="12"/>
+      <x:c r="G37" s="12"/>
+      <x:c r="H37" s="12"/>
+    </x:row>
     <x:row r="38" ht="15.75" customHeight="1"/>
     <x:row r="39" ht="15.75" customHeight="1"/>
     <x:row r="40" ht="15.75" customHeight="1"/>
@@ -2761,6 +2897,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
     <x:row r="1001" ht="15.75" customHeight="1"/>
+    <x:row r="1002" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69888889789581299" right="0.69888889789581299" top="0.75" bottom="0.75" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,128 +19,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="93">
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
   </x:si>
   <x:si>
     <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
   </x:si>
   <x:si>
     <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
 사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
   </x:si>
   <x:si>
+    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
+내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설은 반드시 다시 쓰입니다.
+VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
     <x:t>하루의 시작은 일정 관리부터!
 영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
     <x:t>하루의 시작은 일정 관리부터!
 영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>전설은 반드시 다시 쓰입니다.
-VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
-  </x:si>
-  <x:si>
     <x:t>영웅들의 일정 관리 또한 당신의 업무!
 하루의 일정을 정해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
+사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
   </x:si>
   <x:si>
     <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
@@ -214,10 +145,6 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
-사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
-  </x:si>
-  <x:si>
     <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
 이 모든 것은 영웅들을 위해!</x:t>
   </x:si>
@@ -226,82 +153,79 @@
 영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
     <x:t>Quest_02_05</x:t>
   </x:si>
   <x:si>
-    <x:t>전설적인 서포터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QuestName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
     <x:t>Quest_01_04</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_01_05</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
     <x:t>Room_Sleep</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
+    <x:t>AdvanceDay</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_02_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -330,6 +254,158 @@
       </mc:AlternateContent>
       <x:t>2</x:t>
     </x:r>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
+내일 입소될 영웅들을 확인해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들을 위해!
+전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
+하지만 땅으로 들어갈 수는 있죠!
+굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 많아지면 방이 부족할 수 있습니다.
+방을 더 만들어봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
+영웅들의 일정을 정해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1119,117 +1195,123 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J1" s="4"/>
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="J2" s="2"/>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J3" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="J3" s="8"/>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>24</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1249,31 +1331,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1289,29 +1371,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>58</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1327,29 +1409,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1365,29 +1447,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1403,29 +1485,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>66</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1441,31 +1523,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>42</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1481,31 +1563,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D11" s="10" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="s">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1521,31 +1603,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H12" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1561,31 +1643,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H13" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>61</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1601,29 +1683,29 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1639,29 +1721,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H15" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1676,15 +1758,31 @@
       <x:c r="T15" s="12"/>
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A16" s="2"/>
-      <x:c r="B16" s="2"/>
-      <x:c r="C16" s="2"/>
-      <x:c r="D16" s="2"/>
+      <x:c r="A16" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-      <x:c r="G16" s="2"/>
-      <x:c r="H16" s="2"/>
-      <x:c r="I16" s="12"/>
+      <x:c r="F16" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H16" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
       <x:c r="L16" s="12"/>
@@ -1698,15 +1796,31 @@
       <x:c r="T16" s="12"/>
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
-      <x:c r="A17" s="2"/>
-      <x:c r="B17" s="2"/>
-      <x:c r="C17" s="2"/>
-      <x:c r="D17" s="2"/>
+      <x:c r="A17" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="E17" s="2"/>
-      <x:c r="F17" s="2"/>
-      <x:c r="G17" s="2"/>
-      <x:c r="H17" s="2"/>
-      <x:c r="I17" s="17"/>
+      <x:c r="F17" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H17" s="2">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="I17" s="17" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
       <x:c r="L17" s="12"/>
@@ -1720,60 +1834,127 @@
       <x:c r="T17" s="12"/>
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A18" s="2"/>
-      <x:c r="B18" s="2"/>
-      <x:c r="C18" s="2"/>
-      <x:c r="D18" s="2"/>
+      <x:c r="A18" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="E18" s="2"/>
-      <x:c r="F18" s="2"/>
-      <x:c r="G18" s="2"/>
-      <x:c r="H18" s="2"/>
-      <x:c r="I18" s="12"/>
+      <x:c r="F18" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H18" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I18" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A19" s="2"/>
-      <x:c r="B19" s="2"/>
-      <x:c r="C19" s="2"/>
-      <x:c r="D19" s="2"/>
+      <x:c r="A19" s="2" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="E19" s="2"/>
-      <x:c r="F19" s="2"/>
-      <x:c r="G19" s="2"/>
-      <x:c r="H19" s="2"/>
-      <x:c r="I19" s="17"/>
+      <x:c r="F19" s="2">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H19" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I19" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A20" s="2"/>
-      <x:c r="B20" s="2"/>
-      <x:c r="C20" s="2"/>
+      <x:c r="A20" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="D20" s="2"/>
       <x:c r="E20" s="2"/>
-      <x:c r="F20" s="2"/>
-      <x:c r="G20" s="2"/>
-      <x:c r="H20" s="2"/>
-      <x:c r="I20" s="12"/>
+      <x:c r="F20" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H20" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I20" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A21" s="2"/>
-      <x:c r="B21" s="2"/>
-      <x:c r="C21" s="2"/>
-      <x:c r="D21" s="2"/>
+      <x:c r="A21" s="2" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="s">
+        <x:v>90</x:v>
+      </x:c>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2"/>
       <x:c r="G21" s="2"/>
       <x:c r="H21" s="2"/>
-      <x:c r="I21" s="17"/>
+      <x:c r="I21" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
-    <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A22" s="2"/>
-      <x:c r="B22" s="2"/>
-      <x:c r="C22" s="2"/>
+    <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="A22" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="D22" s="2"/>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2"/>
       <x:c r="G22" s="2"/>
       <x:c r="H22" s="2"/>
-      <x:c r="I22" s="17"/>
+      <x:c r="I22" s="2" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="2"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,63 +19,71 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="93">
-  <x:si>
-    <x:t>연이은 건설2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설1</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
+하지만 땅으로 들어갈 수는 있죠!
+굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
   </x:si>
   <x:si>
     <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
   </x:si>
   <x:si>
     <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
 사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
   </x:si>
   <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
 내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
   </x:si>
   <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
     <x:t>전설은 반드시 다시 쓰입니다.
 VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>영웅들의 일정 관리 또한 당신의 업무!
 하루의 일정을 정해봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
-사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
-사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
+    <x:t>영웅들이 많아지면 방이 부족할 수 있습니다.
+방을 더 만들어봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
+영웅들의 일정을 정해봅시다!</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -145,6 +153,29 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
+사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
+사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들을 위해!
+전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
 이 모든 것은 영웅들을 위해!</x:t>
   </x:si>
@@ -153,79 +184,200 @@
 영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
+내일 입소될 영웅들을 확인해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
     <x:t>Room_Office</x:t>
   </x:si>
   <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>전설적인 서포터</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QuestName</x:t>
+    <x:t>Quest_02_05</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
     <x:t>Quest_02_04</x:t>
   </x:si>
   <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로</x:t>
+  </x:si>
+  <x:si>
     <x:t>Schedule</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_02_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -254,158 +406,6 @@
       </mc:AlternateContent>
       <x:t>2</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
-내일 입소될 영웅들을 확인해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들을 위해!
-전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
-하지만 땅으로 들어갈 수는 있죠!
-굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 많아지면 방이 부족할 수 있습니다.
-방을 더 만들어봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
-영웅들의 일정을 정해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digging</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1195,123 +1195,123 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J3" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1331,31 +1331,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1371,29 +1371,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1409,29 +1409,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1447,29 +1447,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1485,29 +1485,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>42</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1523,31 +1523,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1563,31 +1563,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1603,31 +1603,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H12" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1643,31 +1643,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H13" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>39</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1683,13 +1683,13 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
         <x:v>5</x:v>
@@ -1699,13 +1699,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1721,29 +1721,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H15" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>33</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1759,29 +1759,29 @@
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
@@ -1797,29 +1797,29 @@
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>42</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I17" s="17" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
@@ -1835,125 +1835,141 @@
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>81</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H18" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I18" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I19" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D20" s="2"/>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H20" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I20" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>76</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E21" s="2"/>
-      <x:c r="F21" s="2"/>
-      <x:c r="G21" s="2"/>
-      <x:c r="H21" s="2"/>
+      <x:c r="F21" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H21" s="2">
+        <x:v>300</x:v>
+      </x:c>
       <x:c r="I21" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D22" s="2"/>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="s">
+        <x:v>76</x:v>
+      </x:c>
       <x:c r="E22" s="2"/>
-      <x:c r="F22" s="2"/>
-      <x:c r="G22" s="2"/>
-      <x:c r="H22" s="2"/>
+      <x:c r="F22" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H22" s="2">
+        <x:v>300</x:v>
+      </x:c>
       <x:c r="I22" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,15 +19,153 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
+    <x:t>테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엔딩 테스트용 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로</x:t>
   </x:si>
   <x:si>
     <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
@@ -35,26 +173,19 @@
 굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
     <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
 사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
   </x:si>
   <x:si>
     <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
 영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
   </x:si>
   <x:si>
@@ -62,14 +193,6 @@
 내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
   </x:si>
   <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
     <x:t>전설은 반드시 다시 쓰입니다.
 VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
   </x:si>
@@ -84,6 +207,22 @@
   <x:si>
     <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
 영웅들의 일정을 정해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
+사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들을 위해!
+전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -153,138 +292,92 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
+이 모든 것은 영웅들을 위해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
+내일 입소될 영웅들을 확인해봅시다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
 사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
-사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들을 위해!
-전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
-이 모든 것은 영웅들을 위해!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
-내일 입소될 영웅들을 확인해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digging</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설1</x:t>
+    <x:t>영웅들과의 만남1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_01</x:t>
   </x:si>
   <x:si>
     <x:t>실버타운의 시작</x:t>
   </x:si>
   <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
   </x:si>
   <x:si>
     <x:t>전설적인 영웅들</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
   </x:si>
   <x:si>
     <x:t>BuildRoom</x:t>
@@ -293,91 +386,10 @@
     <x:t>Quest_02_02</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QuestName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueID</x:t>
+    <x:t>Quest_03_01</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_02_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남2</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -1195,123 +1207,123 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J3" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>61</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1331,31 +1343,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="s">
+      <x:c r="D5" s="10" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1371,29 +1383,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1409,29 +1421,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1447,29 +1459,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>13</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>61</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1485,29 +1497,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1523,31 +1535,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>26</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1563,16 +1575,16 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
         <x:v>1</x:v>
@@ -1581,13 +1593,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1603,31 +1615,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H12" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1643,31 +1655,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E13" s="2" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H13" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>63</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1683,29 +1695,29 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1721,29 +1733,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H15" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>73</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1759,29 +1771,29 @@
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
@@ -1797,29 +1809,29 @@
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I17" s="17" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
@@ -1835,153 +1847,164 @@
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H18" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I18" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>61</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I19" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H20" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I20" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I21" s="8" t="s">
-        <x:v>69</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H22" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I22" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A23" s="2"/>
-      <x:c r="B23" s="2"/>
-      <x:c r="C23" s="2"/>
-      <x:c r="D23" s="2"/>
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="A23" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B23" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C23" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2"/>
       <x:c r="G23" s="2"/>
       <x:c r="H23" s="2"/>
       <x:c r="I23" s="12"/>
+      <x:c r="J23" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A24" s="2"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,153 +19,101 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="97">
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digging</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엔딩 테스트용 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
+  <x:si>
+    <x:t>하루의 끝5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들을 위해!
+전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
+위대한 영웅들을 만나봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_07_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬슬 서포터용 아이템이 떨어져가지 않나요?
+아이템을 3개 구매하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_06_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
+사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
+내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
+이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
+영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설은 반드시 다시 쓰입니다.
+VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
+사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
   </x:si>
   <x:si>
     <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
@@ -173,56 +121,12 @@
 굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
-사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
-내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설은 반드시 다시 쓰입니다.
-VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
-  </x:si>
-  <x:si>
     <x:t>영웅들의 일정 관리 또한 당신의 업무!
 하루의 일정을 정해봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들이 많아지면 방이 부족할 수 있습니다.
-방을 더 만들어봅시다!</x:t>
-  </x:si>
-  <x:si>
     <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
 영웅들의 일정을 정해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
-사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들을 위해!
-전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -292,6 +196,15 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
     <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
 이 모든 것은 영웅들을 위해!</x:t>
   </x:si>
@@ -300,93 +213,116 @@
 영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
-내일 입소될 영웅들을 확인해봅시다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
 사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
     <x:t>영웅들과의 만남1</x:t>
   </x:si>
   <x:si>
-    <x:t>Schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터</x:t>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Office</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
     <x:t>Quest_01_01</x:t>
   </x:si>
   <x:si>
     <x:t>실버타운의 시작</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
     <x:t>QuestName</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_02</x:t>
+    <x:t>Quest_03_04</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_01_03</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
+    <x:t>Quest_03_01</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_02_07</x:t>
@@ -418,6 +354,105 @@
       </mc:AlternateContent>
       <x:t>2</x:t>
     </x:r>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -554,7 +589,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -608,6 +643,9 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1191,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:T37"/>
+  <x:dimension ref="A1:T43"/>
   <x:sheetFormatPr defaultColWidth="11.5078125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="17.83984375" style="1" customWidth="1"/>
@@ -1207,123 +1245,123 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J3" s="8" t="s">
-        <x:v>85</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>62</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1343,31 +1381,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>60</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1383,29 +1421,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>59</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1421,29 +1459,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>56</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>82</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1459,29 +1497,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1497,29 +1535,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>67</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1535,31 +1573,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>65</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1575,31 +1613,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1615,31 +1653,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H12" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1655,31 +1693,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>64</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H13" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1695,29 +1733,29 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>84</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1733,29 +1771,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>55</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H15" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>86</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1771,29 +1809,29 @@
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>66</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>74</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
@@ -1809,29 +1847,29 @@
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>54</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I17" s="17" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
@@ -1847,29 +1885,29 @@
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H18" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I18" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
@@ -1877,233 +1915,326 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>57</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I19" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>61</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H20" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I20" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H21" s="2">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="I21" s="8" t="s">
-        <x:v>83</x:v>
+      <x:c r="I21" s="18" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>54</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H22" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I22" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:10" ht="15.75" customHeight="1">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C23" s="2" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D23" s="2" t="s">
+      <x:c r="G23" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H23" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I23" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A24" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B24" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="2"/>
-      <x:c r="G23" s="2"/>
-      <x:c r="H23" s="2"/>
-      <x:c r="I23" s="12"/>
-      <x:c r="J23" s="1" t="s">
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H24" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I24" s="2" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A25" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C25" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G25" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H25" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I25" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A24" s="2"/>
-      <x:c r="B24" s="2"/>
-      <x:c r="C24" s="2"/>
-      <x:c r="D24" s="2"/>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="2"/>
-      <x:c r="G24" s="2"/>
-      <x:c r="H24" s="2"/>
-      <x:c r="I24" s="12"/>
-    </x:row>
-    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A25" s="2"/>
-      <x:c r="B25" s="2"/>
-      <x:c r="C25" s="2"/>
-      <x:c r="D25" s="2"/>
-      <x:c r="E25" s="2"/>
-      <x:c r="F25" s="2"/>
-      <x:c r="G25" s="2"/>
-      <x:c r="H25" s="2"/>
-      <x:c r="I25" s="17"/>
-    </x:row>
     <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A26" s="2"/>
-      <x:c r="B26" s="12"/>
-      <x:c r="C26" s="2"/>
-      <x:c r="D26" s="2"/>
+      <x:c r="A26" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B26" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
       <x:c r="E26" s="2"/>
-      <x:c r="F26" s="2"/>
-      <x:c r="G26" s="2"/>
-      <x:c r="H26" s="2"/>
-      <x:c r="I26" s="12"/>
+      <x:c r="F26" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H26" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I26" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A27" s="12"/>
-      <x:c r="B27" s="12"/>
-      <x:c r="C27" s="12"/>
-      <x:c r="D27" s="12"/>
-      <x:c r="E27" s="12"/>
-      <x:c r="F27" s="12"/>
-      <x:c r="G27" s="12"/>
-      <x:c r="H27" s="12"/>
-      <x:c r="J27" s="12"/>
+      <x:c r="A27" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B27" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H27" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I27" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A28" s="12"/>
-      <x:c r="B28" s="12"/>
-      <x:c r="C28" s="12"/>
-      <x:c r="D28" s="12"/>
-      <x:c r="E28" s="12"/>
-      <x:c r="F28" s="12"/>
-      <x:c r="G28" s="12"/>
-      <x:c r="H28" s="12"/>
-      <x:c r="J28" s="12"/>
-    </x:row>
-    <x:row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A29" s="12"/>
-      <x:c r="B29" s="12"/>
-      <x:c r="C29" s="12"/>
-      <x:c r="D29" s="12"/>
-      <x:c r="E29" s="12"/>
-      <x:c r="F29" s="12"/>
-      <x:c r="G29" s="12"/>
-      <x:c r="H29" s="12"/>
-      <x:c r="J29" s="12"/>
-    </x:row>
-    <x:row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A30" s="12"/>
-      <x:c r="B30" s="12"/>
-      <x:c r="C30" s="12"/>
-      <x:c r="D30" s="12"/>
-      <x:c r="E30" s="12"/>
-      <x:c r="F30" s="12"/>
-      <x:c r="G30" s="12"/>
-      <x:c r="H30" s="12"/>
-      <x:c r="J30" s="12"/>
-    </x:row>
-    <x:row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A31" s="12"/>
-      <x:c r="B31" s="12"/>
-      <x:c r="C31" s="12"/>
-      <x:c r="D31" s="12"/>
-      <x:c r="E31" s="12"/>
-      <x:c r="F31" s="12"/>
-      <x:c r="G31" s="12"/>
-      <x:c r="H31" s="12"/>
-    </x:row>
-    <x:row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A32" s="12"/>
+      <x:c r="A28" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B28" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C28" s="16" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H28" s="2">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I28" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+      <x:c r="I29" s="12"/>
+    </x:row>
+    <x:row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
+      <x:c r="C30" s="2"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+      <x:c r="I30" s="12"/>
+    </x:row>
+    <x:row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+      <x:c r="I31" s="17"/>
+    </x:row>
+    <x:row r="32" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A32" s="2"/>
       <x:c r="B32" s="12"/>
-      <x:c r="C32" s="12"/>
-      <x:c r="D32" s="12"/>
-      <x:c r="E32" s="12"/>
-      <x:c r="F32" s="12"/>
-      <x:c r="G32" s="12"/>
-      <x:c r="H32" s="12"/>
-    </x:row>
-    <x:row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+      <x:c r="I32" s="12"/>
+    </x:row>
+    <x:row r="33" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A33" s="12"/>
       <x:c r="B33" s="12"/>
       <x:c r="C33" s="12"/>
@@ -2112,8 +2243,9 @@
       <x:c r="F33" s="12"/>
       <x:c r="G33" s="12"/>
       <x:c r="H33" s="12"/>
-    </x:row>
-    <x:row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="J33" s="12"/>
+    </x:row>
+    <x:row r="34" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A34" s="12"/>
       <x:c r="B34" s="12"/>
       <x:c r="C34" s="12"/>
@@ -2122,8 +2254,9 @@
       <x:c r="F34" s="12"/>
       <x:c r="G34" s="12"/>
       <x:c r="H34" s="12"/>
-    </x:row>
-    <x:row r="35" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="J34" s="12"/>
+    </x:row>
+    <x:row r="35" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A35" s="12"/>
       <x:c r="B35" s="12"/>
       <x:c r="C35" s="12"/>
@@ -2132,8 +2265,9 @@
       <x:c r="F35" s="12"/>
       <x:c r="G35" s="12"/>
       <x:c r="H35" s="12"/>
-    </x:row>
-    <x:row r="36" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="J35" s="12"/>
+    </x:row>
+    <x:row r="36" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A36" s="12"/>
       <x:c r="B36" s="12"/>
       <x:c r="C36" s="12"/>
@@ -2142,6 +2276,7 @@
       <x:c r="F36" s="12"/>
       <x:c r="G36" s="12"/>
       <x:c r="H36" s="12"/>
+      <x:c r="J36" s="12"/>
     </x:row>
     <x:row r="37" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A37" s="12"/>
@@ -2153,12 +2288,66 @@
       <x:c r="G37" s="12"/>
       <x:c r="H37" s="12"/>
     </x:row>
-    <x:row r="38" ht="15.75" customHeight="1"/>
-    <x:row r="39" ht="15.75" customHeight="1"/>
-    <x:row r="40" ht="15.75" customHeight="1"/>
-    <x:row r="41" ht="15.75" customHeight="1"/>
-    <x:row r="42" ht="15.75" customHeight="1"/>
-    <x:row r="43" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A38" s="12"/>
+      <x:c r="B38" s="12"/>
+      <x:c r="C38" s="12"/>
+      <x:c r="D38" s="12"/>
+      <x:c r="E38" s="12"/>
+      <x:c r="F38" s="12"/>
+      <x:c r="G38" s="12"/>
+      <x:c r="H38" s="12"/>
+    </x:row>
+    <x:row r="39" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A39" s="12"/>
+      <x:c r="B39" s="12"/>
+      <x:c r="C39" s="12"/>
+      <x:c r="D39" s="12"/>
+      <x:c r="E39" s="12"/>
+      <x:c r="F39" s="12"/>
+      <x:c r="G39" s="12"/>
+      <x:c r="H39" s="12"/>
+    </x:row>
+    <x:row r="40" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A40" s="12"/>
+      <x:c r="B40" s="12"/>
+      <x:c r="C40" s="12"/>
+      <x:c r="D40" s="12"/>
+      <x:c r="E40" s="12"/>
+      <x:c r="F40" s="12"/>
+      <x:c r="G40" s="12"/>
+      <x:c r="H40" s="12"/>
+    </x:row>
+    <x:row r="41" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A41" s="12"/>
+      <x:c r="B41" s="12"/>
+      <x:c r="C41" s="12"/>
+      <x:c r="D41" s="12"/>
+      <x:c r="E41" s="12"/>
+      <x:c r="F41" s="12"/>
+      <x:c r="G41" s="12"/>
+      <x:c r="H41" s="12"/>
+    </x:row>
+    <x:row r="42" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A42" s="12"/>
+      <x:c r="B42" s="12"/>
+      <x:c r="C42" s="12"/>
+      <x:c r="D42" s="12"/>
+      <x:c r="E42" s="12"/>
+      <x:c r="F42" s="12"/>
+      <x:c r="G42" s="12"/>
+      <x:c r="H42" s="12"/>
+    </x:row>
+    <x:row r="43" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A43" s="12"/>
+      <x:c r="B43" s="12"/>
+      <x:c r="C43" s="12"/>
+      <x:c r="D43" s="12"/>
+      <x:c r="E43" s="12"/>
+      <x:c r="F43" s="12"/>
+      <x:c r="G43" s="12"/>
+      <x:c r="H43" s="12"/>
+    </x:row>
     <x:row r="44" ht="15.75" customHeight="1"/>
     <x:row r="45" ht="15.75" customHeight="1"/>
     <x:row r="46" ht="15.75" customHeight="1"/>
@@ -3118,6 +3307,12 @@
     <x:row r="1000" ht="15.75" customHeight="1"/>
     <x:row r="1001" ht="15.75" customHeight="1"/>
     <x:row r="1002" ht="15.75" customHeight="1"/>
+    <x:row r="1003" ht="15.75" customHeight="1"/>
+    <x:row r="1004" ht="15.75" customHeight="1"/>
+    <x:row r="1005" ht="15.75" customHeight="1"/>
+    <x:row r="1006" ht="15.75" customHeight="1"/>
+    <x:row r="1007" ht="15.75" customHeight="1"/>
+    <x:row r="1008" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69888889789581299" right="0.69888889789581299" top="0.75" bottom="0.75" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,97 +19,148 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
-  <x:si>
-    <x:t>하루의 끝5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들을 위해!
-전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝4</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="111">
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬슬 서포터용 아이템이 떨어져가지 않나요?
+아이템을 3개 구매하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
+영웅들의 일정을 정해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들의 일정 관리 또한 당신의 업무!
+하루의 일정을 정해봅시다!</x:t>
   </x:si>
   <x:si>
     <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
 위대한 영웅들을 만나봅시다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_07_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬슬 서포터용 아이템이 떨어져가지 않나요?
-아이템을 3개 구매하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_06_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
-사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엔딩 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝4</x:t>
   </x:si>
   <x:si>
     <x:t>하루의 끝7</x:t>
   </x:si>
   <x:si>
-    <x:t>전설적인 서포터2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
-내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
-이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
-영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설은 반드시 다시 쓰입니다.
-VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
   </x:si>
   <x:si>
     <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
@@ -121,12 +172,20 @@
 굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들의 일정 관리 또한 당신의 업무!
-하루의 일정을 정해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
-영웅들의 일정을 정해봅시다!</x:t>
+    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
+사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들을 위해!
+전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -196,13 +255,32 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
+내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
+영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
+이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설은 반드시 다시 쓰입니다.
+VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
   </x:si>
   <x:si>
     <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
@@ -213,8 +291,40 @@
 영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
-사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+    <x:t>Quest_07_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_06_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_02_06</x:t>
@@ -223,88 +333,94 @@
     <x:t>AdvanceDay</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남2</x:t>
+    <x:t>AdmitHero</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_04_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_01_04</x:t>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_05</x:t>
   </x:si>
   <x:si>
     <x:t>Quest_01_05</x:t>
   </x:si>
   <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
     <x:t>Schedule</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Battle</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들과의 만남1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueID</x:t>
-  </x:si>
-  <x:si>
     <x:t>Quest_02_04</x:t>
   </x:si>
   <x:si>
-    <x:t>전설적인 영웅들</x:t>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_07</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Sleep</x:t>
@@ -313,19 +429,7 @@
     <x:t>QuestName</x:t>
   </x:si>
   <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_07</x:t>
+    <x:t>Quest_08_01</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -356,103 +460,8 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digging</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
+    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
+사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1245,123 +1254,123 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>102</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J3" s="8" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>6</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>67</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>500</x:v>
@@ -1381,31 +1390,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>5</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1421,29 +1430,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>52</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1459,29 +1468,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1497,29 +1506,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1535,29 +1544,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>36</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1573,31 +1582,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="D10" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1613,31 +1622,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1653,31 +1662,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D12" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H12" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1693,31 +1702,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>34</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H13" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1733,29 +1742,29 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>65</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1771,29 +1780,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>25</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H15" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>59</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1809,29 +1818,29 @@
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>52</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
@@ -1847,29 +1856,29 @@
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I17" s="17" t="s">
-        <x:v>73</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
@@ -1885,321 +1894,338 @@
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>29</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H18" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I18" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>24</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>56</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I19" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H20" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I20" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>27</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H21" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H22" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I22" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C23" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H23" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I23" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A24" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="D24" s="10" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H24" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I24" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D25" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H25" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I25" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D26" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H26" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I26" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A27" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D27" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E27" s="2"/>
       <x:c r="F27" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H27" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I27" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="16" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E28" s="2"/>
       <x:c r="F28" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H28" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I28" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:9" ht="15.75" customHeight="1">
-      <x:c r="A29" s="2"/>
-      <x:c r="B29" s="2"/>
-      <x:c r="C29" s="2"/>
-      <x:c r="D29" s="2"/>
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="A29" s="2" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="E29" s="2"/>
-      <x:c r="F29" s="2"/>
-      <x:c r="G29" s="2"/>
-      <x:c r="H29" s="2"/>
+      <x:c r="F29" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H29" s="2">
+        <x:v>300</x:v>
+      </x:c>
       <x:c r="I29" s="12"/>
+      <x:c r="J29" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A30" s="2"/>

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -21,150 +21,48 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="111">
   <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
     <x:t>슬슬 서포터용 아이템이 떨어져가지 않나요?
 아이템을 3개 구매하세요!</x:t>
   </x:si>
   <x:si>
+    <x:t>영웅들의 일정 관리 또한 당신의 업무!
+하루의 일정을 정해봅시다!</x:t>
+  </x:si>
+  <x:si>
     <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
 영웅들의 일정을 정해봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들의 일정 관리 또한 당신의 업무!
-하루의 일정을 정해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
-위대한 영웅들을 만나봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엔딩 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digging</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
-사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
+    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
+사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
+내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
+이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설은 반드시 다시 쓰입니다.
+VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
+영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
   </x:si>
   <x:si>
     <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
@@ -172,8 +70,16 @@
 굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
   </x:si>
   <x:si>
-    <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
-사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
+    <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
+사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
+위대한 영웅들을 만나봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
   </x:si>
   <x:si>
     <x:t>이제 업무를 볼 사무실이 필요합니다!
@@ -184,8 +90,200 @@
 전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
+    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
+사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
+이 모든 것은 영웅들을 위해!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_07_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_06_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_08_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">첫 삽을 뜨다 </x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="Times New Roman"/>
+            <x:sz val="10"/>
+            <x:color rgb="ff000000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="Times New Roman"/>
+            <x:sz val="10"/>
+            <x:color rgb="ff000000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>2</x:t>
+    </x:r>
   </x:si>
   <x:si>
     <x:r>
@@ -255,213 +353,115 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
-내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
-영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
-이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설은 반드시 다시 쓰입니다.
-VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
-이 모든 것은 영웅들을 위해!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_07_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_06_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QuestName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_08_01</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t xml:space="preserve">첫 삽을 뜨다 </x:t>
-    </x:r>
-    <x:r>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-          <x:rPr hs:extension="1">
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-            <hs:size val="100"/>
-            <hs:ratio val="100"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:rPr>
-        </mc:Choice>
-        <mc:Fallback>
-          <x:rPr>
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <x:t>2</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
-사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엔딩 테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1254,126 +1254,126 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>94</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J3" s="8" t="s">
-        <x:v>98</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H4" s="2">
-        <x:v>500</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="I4" s="12"/>
       <x:c r="J4" s="12"/>
@@ -1390,31 +1390,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>109</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H5" s="2">
-        <x:v>1000</x:v>
+        <x:v>1300</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1430,29 +1430,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>85</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H6" s="2">
-        <x:v>300</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1468,29 +1468,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H7" s="2">
-        <x:v>300</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1506,29 +1506,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H8" s="2">
-        <x:v>300</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1544,29 +1544,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H9" s="2">
-        <x:v>800</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1582,31 +1582,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>61</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H10" s="2">
-        <x:v>800</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1622,31 +1622,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>54</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H11" s="2">
-        <x:v>800</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1662,31 +1662,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>53</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H12" s="2">
-        <x:v>800</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>93</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1702,31 +1702,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H13" s="2">
-        <x:v>800</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>90</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1742,29 +1742,29 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>48</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>103</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1780,29 +1780,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>59</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H15" s="2">
-        <x:v>800</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>88</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1818,29 +1818,29 @@
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>85</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>74</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
@@ -1856,29 +1856,29 @@
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I17" s="17" t="s">
-        <x:v>105</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
@@ -1894,337 +1894,337 @@
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>99</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H18" s="2">
-        <x:v>300</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="I18" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I19" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="2">
-        <x:v>300</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I20" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H21" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>93</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H22" s="2">
-        <x:v>300</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="I22" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H23" s="2">
-        <x:v>300</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I23" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A24" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="16" t="s">
-        <x:v>58</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="10" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H24" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I24" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H25" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I25" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C26" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H26" s="2">
-        <x:v>300</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="I26" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A27" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C27" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D27" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="2"/>
       <x:c r="F27" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H27" s="2">
-        <x:v>300</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="I27" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C28" s="16" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="2"/>
       <x:c r="F28" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H28" s="2">
-        <x:v>300</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="I28" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A29" s="2" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B29" s="2" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B29" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E29" s="2"/>
       <x:c r="F29" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H29" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I29" s="12"/>
       <x:c r="J29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Quest.xlsx
+++ b/JsonConverter/ExcelFiles/Quest.xlsx
@@ -19,50 +19,237 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="111">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="108">
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필요 횟수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선행 퀘스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대사 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>첫 삽을 뜨다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수행 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새로운 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digging</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퀘스트 내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 끝6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연이은 건설2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_07_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>더 깊은 곳으로1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_06_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdvanceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 서포터2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildRoom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_04_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설의 재구성1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_05_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>실버타운의 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AdmitHero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들의 일정 관리 또한 당신의 업무!
+하루의 일정을 정해봅시다!</x:t>
+  </x:si>
   <x:si>
     <x:t>슬슬 서포터용 아이템이 떨어져가지 않나요?
 아이템을 3개 구매하세요!</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들의 일정 관리 또한 당신의 업무!
-하루의 일정을 정해봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
-영웅들의 일정을 정해봅시다!</x:t>
+    <x:t>ConditionTargetID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PurchaseItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredQuestID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConditionCount</x:t>
   </x:si>
   <x:si>
     <x:t>H.B 프로젝트는 영웅들이 주인공이지만 서포터는 당신입니다.
 사무실에서 당신이 사용할 무기들을 구매하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
-일정에 맞는 방을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
-내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
-이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설은 반드시 다시 쓰입니다.
-VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
-영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
   </x:si>
   <x:si>
     <x:t>아무튼 탈인간 실버타운은 비밀이기에 높이 건물을 쌓을 수 없습니다.
@@ -70,220 +257,68 @@
 굴착을 진행해 더 깊은 곳으로 들어가봅시다!</x:t>
   </x:si>
   <x:si>
+    <x:t>영웅들은 일정을 수행하지 못하면 스트레스를 받습니다.
+일정에 맞는 방을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 위생을 위해 하루 한 번 샤워를 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 하루 한 시간 햇빛을 쬐야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 하루도 굉장히 수고 많으셨습니다!
+내일을 위한 준비를 하도록 하죠. 마감하세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설은 반드시 다시 쓰입니다.
+VR방을 클릭해 영웅들이 전설을 다시 쓸 수 있도록 도와주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방을 건설하다보니 건물이 너무 좁게 느껴지지 않나요?
+이제 돈도 모였겠다 바닥까지 한 번 파봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방이 수용할 수 있는 인원 수는 정해져 있습니다.
+영웅의 이동과 겹치지 않도록 건물을 건설해봅시다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들이 지낼 방이 필요합니다.
+침실 3개를 건설해봅시다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이제 업무를 볼 사무실이 필요합니다!
+사무실을 건설해주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들을 위해!
+전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
+  </x:si>
+  <x:si>
     <x:t>실버타운을 만들었으면 영웅들이 필요하겠죠.
 사무실을 클릭하고 3명의 영웅을 데려옵시다.</x:t>
   </x:si>
   <x:si>
+    <x:t>새로운 영웅을 만났으면 일정을 정해줘야죠.
+영웅들의 일정을 정해봅시다!</x:t>
+  </x:si>
+  <x:si>
     <x:t>이제 새로운 영웅들을 영입할 수 있습니다!
 위대한 영웅들을 만나봅시다.</x:t>
   </x:si>
   <x:si>
-    <x:t>영웅들이 지낼 방이 필요합니다.
-침실 3개를 건설해봅시다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이제 업무를 볼 사무실이 필요합니다!
-사무실을 건설해주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들을 위해!
-전투는 하루에 한 번씩 무조건 해야합니다!</x:t>
-  </x:si>
-  <x:si>
     <x:t>영웅 관리도 중요하지만 실버타운 운영 또한 빼놓을 수 없죠.
 사무실에 들어가 모래시계를 클릭하고 마감합시다!</x:t>
   </x:si>
   <x:si>
+    <x:t>하루의 시작은 일정 관리부터!
+영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>H.B 프로젝트를 위한 VR 방을 건설해봅시다.
 이 모든 것은 영웅들을 위해!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작은 일정 관리부터!
-영웅들은 건강을 위해 7시간 이상 자야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PurchaseItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredQuestID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_07_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_06_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>더 깊은 곳으로1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_05_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설의 재구성1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdvanceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 서포터2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_04_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AdmitHero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>실버타운의 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들과의 만남1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Schedule</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_01_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전설적인 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_03_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QuestName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_08_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quest_02_02</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t xml:space="preserve">첫 삽을 뜨다 </x:t>
-    </x:r>
-    <x:r>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-          <x:rPr hs:extension="1">
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-            <hs:size val="100"/>
-            <hs:ratio val="100"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:rPr>
-        </mc:Choice>
-        <mc:Fallback>
-          <x:rPr>
-            <x:rFont val="Times New Roman"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <x:t>2</x:t>
-    </x:r>
   </x:si>
   <x:si>
     <x:r>
@@ -353,115 +388,71 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>퀘스트 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엔딩 테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필요 횟수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선행 퀘스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digging</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대사 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새로운 영웅들</x:t>
-  </x:si>
-  <x:si>
-    <x:t>퀘스트 내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 시작2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>첫 삽을 뜨다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ending</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수행 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하루의 끝1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연이은 건설2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ConditionTargetID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
+    <x:t>QuestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_02_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_01_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들과의 만남1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quest_03_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전설적인 영웅들</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t xml:space="preserve">첫 삽을 뜨다 </x:t>
+    </x:r>
+    <x:r>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+          <x:rPr hs:extension="1">
+            <x:rFont val="Times New Roman"/>
+            <x:sz val="10"/>
+            <x:color rgb="ff000000"/>
+            <hs:size val="100"/>
+            <hs:ratio val="100"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:rPr>
+        </mc:Choice>
+        <mc:Fallback>
+          <x:rPr>
+            <x:rFont val="Times New Roman"/>
+            <x:sz val="10"/>
+            <x:color rgb="ff000000"/>
+          </x:rPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <x:t>2</x:t>
+    </x:r>
   </x:si>
 </x:sst>
 </file>
@@ -1254,123 +1245,123 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:11" s="9" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H3" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J3" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
     <x:row r="4" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="15" t="s">
-        <x:v>14</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E4" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H4" s="2">
         <x:v>800</x:v>
@@ -1390,31 +1381,31 @@
     </x:row>
     <x:row r="5" spans="1:20" ht="27" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C5" s="15" t="s">
-        <x:v>15</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H5" s="2">
         <x:v>1300</x:v>
       </x:c>
       <x:c r="I5" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J5" s="12"/>
       <x:c r="K5" s="2"/>
@@ -1430,29 +1421,29 @@
     </x:row>
     <x:row r="6" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C6" s="15" t="s">
-        <x:v>12</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H6" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>62</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J6" s="12"/>
       <x:c r="K6" s="12"/>
@@ -1468,29 +1459,29 @@
     </x:row>
     <x:row r="7" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="15" t="s">
-        <x:v>1</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H7" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J7" s="12"/>
       <x:c r="K7" s="12"/>
@@ -1506,29 +1497,29 @@
     </x:row>
     <x:row r="8" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>4</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H8" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J8" s="12"/>
       <x:c r="K8" s="12"/>
@@ -1544,29 +1535,29 @@
     </x:row>
     <x:row r="9" spans="1:20" ht="32.25" customHeight="1">
       <x:c r="A9" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H9" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J9" s="12"/>
       <x:c r="K9" s="12"/>
@@ -1582,31 +1573,31 @@
     </x:row>
     <x:row r="10" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="16" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H10" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J10" s="12"/>
       <x:c r="K10" s="12"/>
@@ -1622,31 +1613,31 @@
     </x:row>
     <x:row r="11" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="16" t="s">
-        <x:v>5</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H11" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="12"/>
       <x:c r="K11" s="12"/>
@@ -1662,31 +1653,31 @@
     </x:row>
     <x:row r="12" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A12" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H12" s="2">
         <x:v>900</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J12" s="12"/>
       <x:c r="K12" s="12"/>
@@ -1702,31 +1693,31 @@
     </x:row>
     <x:row r="13" spans="1:20" ht="26.25" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C13" s="16" t="s">
-        <x:v>18</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H13" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I13" s="17" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J13" s="12"/>
       <x:c r="K13" s="12"/>
@@ -1742,29 +1733,29 @@
     </x:row>
     <x:row r="14" spans="1:20" ht="27.75" customHeight="1">
       <x:c r="A14" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H14" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I14" s="17" t="s">
-        <x:v>64</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J14" s="12"/>
       <x:c r="K14" s="12"/>
@@ -1780,29 +1771,29 @@
     </x:row>
     <x:row r="15" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C15" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="2"/>
       <x:c r="F15" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H15" s="2">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="I15" s="17" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J15" s="12"/>
       <x:c r="K15" s="12"/>
@@ -1818,29 +1809,29 @@
     </x:row>
     <x:row r="16" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A16" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="D16" s="10" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E16" s="2"/>
       <x:c r="F16" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H16" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I16" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J16" s="12"/>
       <x:c r="K16" s="12"/>
@@ -1856,29 +1847,29 @@
     </x:row>
     <x:row r="17" spans="1:20" ht="15.75" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D17" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H17" s="2">
         <x:v>800</x:v>
       </x:c>
       <x:c r="I17" s="17" t="s">
-        <x:v>67</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J17" s="12"/>
       <x:c r="K17" s="12"/>
@@ -1894,338 +1885,321 @@
     </x:row>
     <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B18" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>2</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>60</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H18" s="2">
         <x:v>550</x:v>
       </x:c>
       <x:c r="I18" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C19" s="16" t="s">
-        <x:v>10</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D19" s="10" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E19" s="2"/>
       <x:c r="F19" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H19" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I19" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A20" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E20" s="2"/>
       <x:c r="F20" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H20" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I20" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="16" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="2"/>
       <x:c r="F21" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I21" s="18" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J21" s="12"/>
     </x:row>
     <x:row r="22" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A22" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D22" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E22" s="2"/>
       <x:c r="F22" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H22" s="2">
         <x:v>500</x:v>
       </x:c>
       <x:c r="I22" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="16" t="s">
-        <x:v>0</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H23" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I23" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A24" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C24" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D24" s="10" t="s">
-        <x:v>87</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H24" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I24" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D25" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E25" s="2"/>
       <x:c r="F25" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H25" s="2">
         <x:v>300</x:v>
       </x:c>
       <x:c r="I25" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C26" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D26" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H26" s="2">
         <x:v>600</x:v>
       </x:c>
       <x:c r="I26" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A27" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C27" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D27" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E27" s="2"/>
       <x:c r="F27" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H27" s="2">
         <x:v>400</x:v>
       </x:c>
       <x:c r="I27" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C28" s="16" t="s">
-        <x:v>7</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D28" s="10" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E28" s="2"/>
       <x:c r="F28" s="2">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H28" s="2">
         <x:v>400</x:v>
       </x:c>
       <x:c r="I28" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <x:c r="A29" s="2" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B29" s="2" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C29" s="2" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D29" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
       <x:c r="E29" s="2"/>
-      <x:c r="F29" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="2" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H29" s="2">
-        <x:v>300</x:v>
-      </x:c>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
       <x:c r="I29" s="12"/>
-      <x:c r="J29" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
     </x:row>
     <x:row r="30" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A30" s="2"/>
